--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -637,15 +637,29 @@
           <t>policy_rate_pct</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="2" t="n">
+        <v>4.25</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NBRNM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30-Sep-26</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -741,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>53.1</v>
+        <v>55.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -750,22 +764,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>Q1-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Ministry of Finance</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Mar-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>public debt % GDP</t>
         </is>
       </c>
     </row>
@@ -949,7 +963,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5.804</v>
+        <v>5.51</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,22 +972,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>NBRNM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>gross reserves EUR 5,101m (~USD 5.51bn)</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1015,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.566</v>
+        <v>4.2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1010,24 +1024,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>NBRNM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>31-Aug-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1121,15 +1131,29 @@
           <t>eurobonds_outstanding_usd_bn</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>2.16</v>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ministry of Finance</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1211,6 +1235,21 @@
           <t>fitch</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BB+</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>11-Sep-26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1218,6 +1257,21 @@
           <t>sp</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>02-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1230,6 +1284,24 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PLL concluded Nov-24</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Nov-22</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>moderate</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1258,6 +1330,11 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1268,7 +1345,8 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1276,7 +1354,8 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1284,7 +1363,8 @@
           <t>cpi_avg_pct</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1292,7 +1372,8 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1300,7 +1381,8 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1308,7 +1390,8 @@
           <t>primary_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1316,7 +1399,14 @@
           <t>gov_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" s="2" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Q1-26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1324,7 +1414,8 @@
           <t>external_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1332,7 +1423,14 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NBRNM, Aug-26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1340,7 +1438,8 @@
           <t>revenue_pct_gdp</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1348,7 +1447,8 @@
           <t>interest_pct_revenue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -685,16 +685,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>2.5729</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
+++ b/models/sovereigns/North_Macedonia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/north-macedonia.json</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
